--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00932-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00932-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A34F1A01-13B7-489D-848A-15F6180AFD17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B660342C-D171-4CA1-B5A9-C087624002F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{B08FEA4A-40C8-4A00-AE98-938341D842C5}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{A7FD8F8E-4EA5-4D5D-8D82-117B6700F156}"/>
   </bookViews>
   <sheets>
     <sheet name="00932-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1519,20 +1519,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09C5BECC-0AA8-4E19-8CE0-B2800830C6B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0731AF3-A10E-42FD-B2D8-D83611ECB5E4}">
   <dimension ref="A1:R17"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1560,7 +1560,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1590,7 +1590,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1686,7 +1686,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1766,7 +1766,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2100,7 +2100,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>9.84</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="49" t="s">
         <v>44</v>
       </c>
